--- a/OneDrive/Documents/Exceltodb-post_data/Exceltodb-post_data/output/output.xlsx
+++ b/OneDrive/Documents/Exceltodb-post_data/Exceltodb-post_data/output/output.xlsx
@@ -413,205 +413,268 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:AZ1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Unnamed: 0_x</t>
+          <t>product_id</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>order_id</t>
+          <t>Unnamed: 0.15_x</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>customer_id_x</t>
+          <t>Unnamed: 0.14_x</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>order_date_x</t>
+          <t>Unnamed: 0.13_x</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Unnamed: 0_y</t>
+          <t>Unnamed: 0.12_x</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>customer_id_y</t>
+          <t>Unnamed: 0.11_x</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>order_date_y</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>0</v>
-      </c>
-      <c r="B2" t="n">
-        <v>101</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-01-10</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>2026-01-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="n">
-        <v>102</v>
-      </c>
-      <c r="C3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-01-11</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>2026-01-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="n">
-        <v>103</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="n">
-        <v>104</v>
-      </c>
-      <c r="C5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-01-18</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F5" t="n">
-        <v>3</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2026-01-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" t="n">
-        <v>105</v>
-      </c>
-      <c r="C6" t="n">
-        <v>5</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-01-20</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>4</v>
-      </c>
-      <c r="F6" t="n">
-        <v>5</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>2026-01-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" t="n">
-        <v>106</v>
-      </c>
-      <c r="C7" t="n">
-        <v>7</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-01-25</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>5</v>
-      </c>
-      <c r="F7" t="n">
-        <v>7</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2026-01-25</t>
+          <t>Unnamed: 0.10_x</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.9_x</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.8_x</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.7_x</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.6_x</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.5_x</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.4_x</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.3_x</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.2_x</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.1_x</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>product_name_x</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>category_x</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.15_y</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.14_y</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.13_y</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.12_y</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.11_y</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.10_y</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.9_y</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.8_y</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.7_y</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.6_y</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.5_y</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.4_y</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.3_y</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.2_y</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.1_y</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>product_name_y</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>category_y</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.15</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.14</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.13</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.12</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.11</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.10</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.9</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.8</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.7</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.6</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.5</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.4</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.3</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.2</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.1</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>product_name</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>category</t>
         </is>
       </c>
     </row>

--- a/OneDrive/Documents/Exceltodb-post_data/Exceltodb-post_data/output/output.xlsx
+++ b/OneDrive/Documents/Exceltodb-post_data/Exceltodb-post_data/output/output.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ1"/>
+  <dimension ref="A1:BO1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,255 +424,330 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>Unnamed: 0.20_x</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.19_x</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.18_x</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.17_x</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.16_x</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>Unnamed: 0.15_x</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Unnamed: 0.14_x</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Unnamed: 0.13_x</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Unnamed: 0.12_x</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Unnamed: 0.11_x</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Unnamed: 0.10_x</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Unnamed: 0.9_x</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Unnamed: 0.8_x</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Unnamed: 0.7_x</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Unnamed: 0.6_x</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Unnamed: 0.5_x</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Unnamed: 0.4_x</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Unnamed: 0.3_x</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Unnamed: 0.2_x</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Unnamed: 0.1_x</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>product_name_x</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>category_x</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.20_y</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.19_y</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.18_y</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.17_y</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.16_y</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Unnamed: 0.15_y</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Unnamed: 0.14_y</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Unnamed: 0.13_y</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Unnamed: 0.12_y</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Unnamed: 0.11_y</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Unnamed: 0.10_y</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Unnamed: 0.9_y</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Unnamed: 0.8_y</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Unnamed: 0.7_y</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Unnamed: 0.6_y</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>Unnamed: 0.5_y</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>Unnamed: 0.4_y</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>Unnamed: 0.3_y</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>Unnamed: 0.2_y</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>Unnamed: 0.1_y</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>product_name_y</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>category_y</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.20</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.19</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.18</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.17</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.16</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
         <is>
           <t>Unnamed: 0.15</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>Unnamed: 0.14</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>Unnamed: 0.13</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>Unnamed: 0.12</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>Unnamed: 0.11</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>Unnamed: 0.10</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>Unnamed: 0.9</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>Unnamed: 0.8</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>Unnamed: 0.7</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>Unnamed: 0.6</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>Unnamed: 0.5</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>Unnamed: 0.4</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>Unnamed: 0.3</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>Unnamed: 0.2</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>Unnamed: 0.1</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>product_name</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>category</t>
         </is>

--- a/OneDrive/Documents/Exceltodb-post_data/Exceltodb-post_data/output/output.xlsx
+++ b/OneDrive/Documents/Exceltodb-post_data/Exceltodb-post_data/output/output.xlsx
@@ -413,268 +413,413 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ1"/>
+  <dimension ref="A1:CC1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Unnamed: 0_x</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>product_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.15_x</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Unnamed: 0.14_x</t>
+          <t>Unnamed: 0_y</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Unnamed: 0.13_x</t>
+          <t>Unnamed: 0.1</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Unnamed: 0.12_x</t>
+          <t>Unnamed: 0.10</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Unnamed: 0.11_x</t>
+          <t>Unnamed: 0.11</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Unnamed: 0.10_x</t>
+          <t>Unnamed: 0.12</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Unnamed: 0.9_x</t>
+          <t>Unnamed: 0.13</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Unnamed: 0.8_x</t>
+          <t>Unnamed: 0.14</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Unnamed: 0.7_x</t>
+          <t>Unnamed: 0.15</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Unnamed: 0.6_x</t>
+          <t>Unnamed: 0.16</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Unnamed: 0.5_x</t>
+          <t>Unnamed: 0.17</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Unnamed: 0.4_x</t>
+          <t>Unnamed: 0.18</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>Unnamed: 0.3_x</t>
+          <t>Unnamed: 0.19</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>Unnamed: 0.2_x</t>
+          <t>Unnamed: 0.2</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>Unnamed: 0.1_x</t>
+          <t>Unnamed: 0.20</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>product_name_x</t>
+          <t>Unnamed: 0.21</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>category_x</t>
+          <t>Unnamed: 0.22</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>Unnamed: 0.15_y</t>
+          <t>Unnamed: 0.23</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>Unnamed: 0.14_y</t>
+          <t>Unnamed: 0.24</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>Unnamed: 0.13_y</t>
+          <t>Unnamed: 0.25</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>Unnamed: 0.12_y</t>
+          <t>Unnamed: 0.26</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Unnamed: 0.11_y</t>
+          <t>Unnamed: 0.27</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Unnamed: 0.10_y</t>
+          <t>Unnamed: 0.28</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>Unnamed: 0.9_y</t>
+          <t>Unnamed: 0.29</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Unnamed: 0.8_y</t>
+          <t>Unnamed: 0.3</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>Unnamed: 0.7_y</t>
+          <t>Unnamed: 0.30</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>Unnamed: 0.6_y</t>
+          <t>Unnamed: 0.31</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>Unnamed: 0.5_y</t>
+          <t>Unnamed: 0.32</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>Unnamed: 0.4_y</t>
+          <t>Unnamed: 0.33</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>Unnamed: 0.3_y</t>
+          <t>Unnamed: 0.34</t>
         </is>
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>Unnamed: 0.2_y</t>
+          <t>Unnamed: 0.35</t>
         </is>
       </c>
       <c r="AG1" t="inlineStr">
         <is>
-          <t>Unnamed: 0.1_y</t>
+          <t>Unnamed: 0.36</t>
         </is>
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>product_name_y</t>
+          <t>Unnamed: 0.37</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
         <is>
-          <t>category_y</t>
+          <t>Unnamed: 0.38</t>
         </is>
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Unnamed: 0.15</t>
+          <t>Unnamed: 0.39</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
         <is>
-          <t>Unnamed: 0.14</t>
+          <t>Unnamed: 0.4</t>
         </is>
       </c>
       <c r="AL1" t="inlineStr">
         <is>
-          <t>Unnamed: 0.13</t>
+          <t>Unnamed: 0.40</t>
         </is>
       </c>
       <c r="AM1" t="inlineStr">
         <is>
-          <t>Unnamed: 0.12</t>
+          <t>Unnamed: 0.41</t>
         </is>
       </c>
       <c r="AN1" t="inlineStr">
         <is>
-          <t>Unnamed: 0.11</t>
+          <t>Unnamed: 0.42</t>
         </is>
       </c>
       <c r="AO1" t="inlineStr">
         <is>
-          <t>Unnamed: 0.10</t>
+          <t>Unnamed: 0.43</t>
         </is>
       </c>
       <c r="AP1" t="inlineStr">
         <is>
+          <t>Unnamed: 0.44</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.45</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.46</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.47</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.48</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.49</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.5</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.50</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.51</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.52</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.53</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.54</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.55</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.56</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.57</t>
+        </is>
+      </c>
+      <c r="BE1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.58</t>
+        </is>
+      </c>
+      <c r="BF1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.59</t>
+        </is>
+      </c>
+      <c r="BG1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.6</t>
+        </is>
+      </c>
+      <c r="BH1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.60</t>
+        </is>
+      </c>
+      <c r="BI1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.61</t>
+        </is>
+      </c>
+      <c r="BJ1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.62</t>
+        </is>
+      </c>
+      <c r="BK1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.63</t>
+        </is>
+      </c>
+      <c r="BL1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.64</t>
+        </is>
+      </c>
+      <c r="BM1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.65</t>
+        </is>
+      </c>
+      <c r="BN1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.66</t>
+        </is>
+      </c>
+      <c r="BO1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.67</t>
+        </is>
+      </c>
+      <c r="BP1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.68</t>
+        </is>
+      </c>
+      <c r="BQ1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.69</t>
+        </is>
+      </c>
+      <c r="BR1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.7</t>
+        </is>
+      </c>
+      <c r="BS1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.70</t>
+        </is>
+      </c>
+      <c r="BT1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.71</t>
+        </is>
+      </c>
+      <c r="BU1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.72</t>
+        </is>
+      </c>
+      <c r="BV1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.73</t>
+        </is>
+      </c>
+      <c r="BW1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.74</t>
+        </is>
+      </c>
+      <c r="BX1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.75</t>
+        </is>
+      </c>
+      <c r="BY1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.76</t>
+        </is>
+      </c>
+      <c r="BZ1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.8</t>
+        </is>
+      </c>
+      <c r="CA1" t="inlineStr">
+        <is>
           <t>Unnamed: 0.9</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.8</t>
-        </is>
-      </c>
-      <c r="AR1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.7</t>
-        </is>
-      </c>
-      <c r="AS1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.6</t>
-        </is>
-      </c>
-      <c r="AT1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.5</t>
-        </is>
-      </c>
-      <c r="AU1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.4</t>
-        </is>
-      </c>
-      <c r="AV1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.3</t>
-        </is>
-      </c>
-      <c r="AW1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.2</t>
-        </is>
-      </c>
-      <c r="AX1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.1</t>
-        </is>
-      </c>
-      <c r="AY1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="CC1" t="inlineStr">
         <is>
           <t>product_name</t>
-        </is>
-      </c>
-      <c r="AZ1" t="inlineStr">
-        <is>
-          <t>category</t>
         </is>
       </c>
     </row>

--- a/OneDrive/Documents/Exceltodb-post_data/Exceltodb-post_data/output/output.xlsx
+++ b/OneDrive/Documents/Exceltodb-post_data/Exceltodb-post_data/output/output.xlsx
@@ -413,413 +413,136 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CC1"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Unnamed: 0_x</t>
+          <t>Unnamed: 0</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>product_id</t>
+          <t>city</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Unnamed: 0_y</t>
+          <t>customer_id</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Unnamed: 0.1</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.10</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.11</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.12</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.13</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.14</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.15</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.16</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.17</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.18</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.19</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.2</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.20</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.21</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.22</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.23</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.24</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.25</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.26</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.27</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.28</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.29</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.3</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.30</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.31</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.32</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.33</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.34</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.35</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.36</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.37</t>
-        </is>
-      </c>
-      <c r="AI1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.38</t>
-        </is>
-      </c>
-      <c r="AJ1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.39</t>
-        </is>
-      </c>
-      <c r="AK1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.4</t>
-        </is>
-      </c>
-      <c r="AL1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.40</t>
-        </is>
-      </c>
-      <c r="AM1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.41</t>
-        </is>
-      </c>
-      <c r="AN1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.42</t>
-        </is>
-      </c>
-      <c r="AO1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.43</t>
-        </is>
-      </c>
-      <c r="AP1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.44</t>
-        </is>
-      </c>
-      <c r="AQ1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.45</t>
-        </is>
-      </c>
-      <c r="AR1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.46</t>
-        </is>
-      </c>
-      <c r="AS1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.47</t>
-        </is>
-      </c>
-      <c r="AT1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.48</t>
-        </is>
-      </c>
-      <c r="AU1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.49</t>
-        </is>
-      </c>
-      <c r="AV1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.5</t>
-        </is>
-      </c>
-      <c r="AW1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.50</t>
-        </is>
-      </c>
-      <c r="AX1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.51</t>
-        </is>
-      </c>
-      <c r="AY1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.52</t>
-        </is>
-      </c>
-      <c r="AZ1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.53</t>
-        </is>
-      </c>
-      <c r="BA1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.54</t>
-        </is>
-      </c>
-      <c r="BB1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.55</t>
-        </is>
-      </c>
-      <c r="BC1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.56</t>
-        </is>
-      </c>
-      <c r="BD1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.57</t>
-        </is>
-      </c>
-      <c r="BE1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.58</t>
-        </is>
-      </c>
-      <c r="BF1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.59</t>
-        </is>
-      </c>
-      <c r="BG1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.6</t>
-        </is>
-      </c>
-      <c r="BH1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.60</t>
-        </is>
-      </c>
-      <c r="BI1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.61</t>
-        </is>
-      </c>
-      <c r="BJ1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.62</t>
-        </is>
-      </c>
-      <c r="BK1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.63</t>
-        </is>
-      </c>
-      <c r="BL1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.64</t>
-        </is>
-      </c>
-      <c r="BM1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.65</t>
-        </is>
-      </c>
-      <c r="BN1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.66</t>
-        </is>
-      </c>
-      <c r="BO1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.67</t>
-        </is>
-      </c>
-      <c r="BP1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.68</t>
-        </is>
-      </c>
-      <c r="BQ1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.69</t>
-        </is>
-      </c>
-      <c r="BR1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.7</t>
-        </is>
-      </c>
-      <c r="BS1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.70</t>
-        </is>
-      </c>
-      <c r="BT1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.71</t>
-        </is>
-      </c>
-      <c r="BU1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.72</t>
-        </is>
-      </c>
-      <c r="BV1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.73</t>
-        </is>
-      </c>
-      <c r="BW1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.74</t>
-        </is>
-      </c>
-      <c r="BX1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.75</t>
-        </is>
-      </c>
-      <c r="BY1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.76</t>
-        </is>
-      </c>
-      <c r="BZ1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.8</t>
-        </is>
-      </c>
-      <c r="CA1" t="inlineStr">
-        <is>
-          <t>Unnamed: 0.9</t>
-        </is>
-      </c>
-      <c r="CB1" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="CC1" t="inlineStr">
-        <is>
-          <t>product_name</t>
+          <t>customer_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Alice</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Bob</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dallas</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Charlie</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Seattle</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Diana</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Ethan</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Miami</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Fiona</t>
         </is>
       </c>
     </row>

--- a/OneDrive/Documents/Exceltodb-post_data/Exceltodb-post_data/output/output.xlsx
+++ b/OneDrive/Documents/Exceltodb-post_data/Exceltodb-post_data/output/output.xlsx
@@ -413,26 +413,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Unnamed: 0</t>
+          <t>customer_id</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>order_date</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>order_id</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>city</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>customer_id</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>customer_name</t>
         </is>
@@ -440,17 +445,22 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>101</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Alice</t>
         </is>
@@ -462,15 +472,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>103</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Bob</t>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Alice</t>
         </is>
       </c>
     </row>
@@ -480,15 +495,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>2026-01-11</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>102</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Charlie</t>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Bob</t>
         </is>
       </c>
     </row>
@@ -498,15 +518,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>104</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Diana</t>
+          <t>Dallas</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Charlie</t>
         </is>
       </c>
     </row>
@@ -514,17 +539,16 @@
       <c r="A6" t="n">
         <v>4</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Boston</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>5</v>
-      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>Seattle</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Diana</t>
         </is>
       </c>
     </row>
@@ -534,17 +558,54 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>105</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Ethan</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>Miami</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>6</v>
-      </c>
-      <c r="D7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Fiona</t>
         </is>
       </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>106</v>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/OneDrive/Documents/Exceltodb-post_data/Exceltodb-post_data/output/output.xlsx
+++ b/OneDrive/Documents/Exceltodb-post_data/Exceltodb-post_data/output/output.xlsx
@@ -413,31 +413,61 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>customer_id</t>
+          <t>customer_id_x</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>order_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>remarks</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>product_id</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>product_name</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>quantity</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>customer_id_y</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>order_date</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>order_id</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>city</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>customer_name</t>
         </is>
@@ -445,167 +475,1084 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-01-10</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>101</v>
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>New York</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Alice</t>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Seattle</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Diana</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>103</v>
+        <v>0</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>New York</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Alice</t>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Miami</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Fiona</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-01-11</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>102</v>
+        <v>1</v>
+      </c>
+      <c r="B4" t="n">
+        <v>101</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Delivered successfully</t>
+        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Chicago</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Bob</t>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1001</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Laptop</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Alice</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-01-18</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>104</v>
+        <v>1</v>
+      </c>
+      <c r="B5" t="n">
+        <v>101</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Delivered successfully</t>
+        </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Dallas</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Charlie</t>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1002</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mouse</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Alice</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="B6" t="n">
+        <v>102</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Payment pending</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Seattle</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Diana</t>
+          <t>Furniture</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1003</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Bob</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-01-20</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>105</v>
+        <v>1</v>
+      </c>
+      <c r="B7" t="n">
+        <v>103</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Delayed due to weather</t>
+        </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Boston</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Ethan</t>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1005</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Headphones</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Alice</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="B8" t="n">
+        <v>104</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Returned by customer</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Miami</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Fiona</t>
+          <t>Furniture</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1004</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Chair</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>4</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Dallas</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Charlie</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" t="n">
+        <v>105</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Out for delivery</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1002</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mouse</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" t="n">
+        <v>5</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Ethan</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
         <v>7</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="n">
+        <v>106</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Customer not found</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>9999</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>7</v>
+      </c>
+      <c r="I10" t="inlineStr">
         <is>
           <t>2026-01-25</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>106</v>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" t="n">
+        <v>107</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Order confirmed</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>3</v>
+      </c>
+      <c r="B12" t="n">
+        <v>108</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Packed for shipment</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B13" t="n">
+        <v>109</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Shipped</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>110</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>In transit</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>111</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1</v>
+      </c>
+      <c r="B16" t="n">
+        <v>112</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Awaiting payment</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" t="n">
+        <v>113</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Cancelled by customer</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>3</v>
+      </c>
+      <c r="B18" t="n">
+        <v>114</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Refund initiated</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>4</v>
+      </c>
+      <c r="B19" t="n">
+        <v>115</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Replacement dispatched</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>116</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Delivery failed</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>6</v>
+      </c>
+      <c r="B21" t="n">
+        <v>117</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Rescheduled delivery</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1</v>
+      </c>
+      <c r="B22" t="n">
+        <v>118</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Order on hold</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" t="n">
+        <v>119</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Quality check completed</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" t="n">
+        <v>120</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ready for pickup</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
